--- a/consent_forms/044_third_party_legal_collaboration_consent_form--consent_forms.xlsx
+++ b/consent_forms/044_third_party_legal_collaboration_consent_form--consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1033,8 +1033,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="49" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1062,12 +1062,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'client'}</t>
+          <t>client</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Client'}</t>
+          <t>Client</t>
         </is>
       </c>
     </row>
@@ -1079,12 +1079,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'attorney'}</t>
+          <t>attorney</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Attorney'}</t>
+          <t>Attorney</t>
         </is>
       </c>
     </row>
@@ -1096,12 +1096,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1113,12 +1113,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'to_obtain_legal_opinion'}</t>
+          <t>to_obtain_legal_opinion</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'To obtain legal opinion'}</t>
+          <t>To obtain legal opinion</t>
         </is>
       </c>
     </row>
@@ -1130,12 +1130,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'to_obtain_legal_advice'}</t>
+          <t>to_obtain_legal_advice</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'To obtain legal advice'}</t>
+          <t>To obtain legal advice</t>
         </is>
       </c>
     </row>
@@ -1147,12 +1147,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'to_obtain_information'}</t>
+          <t>to_obtain_information</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'To obtain information'}</t>
+          <t>To obtain information</t>
         </is>
       </c>
     </row>
@@ -1164,12 +1164,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1181,12 +1181,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1198,12 +1198,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1215,12 +1215,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'mail'}</t>
+          <t>mail</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Mail'}</t>
+          <t>Mail</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1249,12 +1249,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1266,12 +1266,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1283,12 +1283,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1300,12 +1300,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1317,12 +1317,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'yes'}</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Yes'}</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1334,12 +1334,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'no'}</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'No'}</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1351,12 +1351,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'yes'}</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'Yes'}</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1368,12 +1368,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'no'}</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'No'}</t>
+          <t>No</t>
         </is>
       </c>
     </row>
